--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
@@ -200,7 +200,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" refreshedBy="Jan Havlíček" refreshedDate="44998.03509409722" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{E2478FBC-AC52-430F-B47A-D78C60D7729B}" mc:Ignorable="xr">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="0" refreshedBy="Jan Havlíček" refreshedDate="44998.03509409722" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{E2478FBC-AC52-430F-B47A-D78C60D7729B}" mc:Ignorable="xr">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:J11" sheet="Data"/>
   </x:cacheSource>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
@@ -87,6 +87,66 @@
   </x:si>
   <x:si>
     <x:t>Content of the table is not important. All fields must be used, in order to save values as shared items</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4:30:00 PM Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1/1/1900 Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1/1/1900 12:30 Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12/24/2020 Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(blank)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(blank) Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.1 Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45000 Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.5 Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUE Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABC Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#DIV/0!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#DIV/0! Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8/10/2020 Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Row Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#N/A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#REF!</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -137,7 +197,7 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -152,6 +212,12 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="19" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -1263,6 +1329,264 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="B3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="B4" s="12">
+        <x:v>0.6875</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H4" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L4" s="13">
+        <x:v>1.52083333333333</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="P4" s="1">
+        <x:v>44189</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="T4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="AG4" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="B5" s="12">
+        <x:v>0.6875</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H5" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L5" s="13">
+        <x:v>1.52083333333333</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="P5" s="1">
+        <x:v>44189</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="T5" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="V5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="W5" s="0">
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="Y5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Z5" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="AF5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="B6" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>14.5</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="T6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="U6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="X6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Z6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AA6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="AB6" s="12">
+        <x:v>0.6875</x:v>
+      </x:c>
+      <x:c r="AC6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="AD6" s="1">
+        <x:v>44053</x:v>
+      </x:c>
+      <x:c r="AE6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="P7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="T7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="W7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="Z7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="AB7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="AD7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A8" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A9" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A10" s="8">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A11" s="9">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A12" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A13" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A14" s="8">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A15" s="9">
+        <x:v>14.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A16" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A17" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A18" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A19" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A20" s="8" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A21" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A22" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:33" x14ac:dyDescent="0.25">
+      <x:c r="A23" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/VariousDataTypesInTableColumns/output.xlsx
@@ -760,7 +760,7 @@
       <x v="4"/>
     </i>
   </colItems>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
